--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:37</t>
+    <t xml:space="preserve">2026-09-09 22:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:23</t>
+    <t xml:space="preserve">2026-09-12 19:40</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:40</t>
+    <t xml:space="preserve">2026-09-24 00:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>90.05</v>
+        <v>40.4</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>65.08</v>
+        <v>28.01</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>52.22</v>
+        <v>21.56</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>45.54</v>
+        <v>20.52</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>45.39</v>
+        <v>19.93</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>30.13</v>
+        <v>13.33</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>29.49</v>
+        <v>12.22</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>26.32</v>
+        <v>11.02</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>21.48</v>
+        <v>8.81</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:17</t>
+    <t xml:space="preserve">2026-09-27 22:07</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:07</t>
+    <t xml:space="preserve">2026-09-29 11:01</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -505,7 +505,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>40.4</v>
+        <v>404.04</v>
       </c>
     </row>
     <row r="3">
@@ -522,7 +522,7 @@
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>28.01</v>
+        <v>280.06</v>
       </c>
     </row>
     <row r="4">
@@ -539,7 +539,7 @@
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>21.56</v>
+        <v>215.65</v>
       </c>
     </row>
     <row r="5">
@@ -556,7 +556,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>20.52</v>
+        <v>205.18</v>
       </c>
     </row>
     <row r="6">
@@ -573,7 +573,7 @@
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>19.93</v>
+        <v>199.27</v>
       </c>
     </row>
     <row r="7">
@@ -590,7 +590,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>13.33</v>
+        <v>133.35</v>
       </c>
     </row>
     <row r="8">
@@ -607,7 +607,7 @@
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>12.22</v>
+        <v>122.23</v>
       </c>
     </row>
     <row r="9">
@@ -624,7 +624,7 @@
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>11.02</v>
+        <v>110.16</v>
       </c>
     </row>
     <row r="10">
@@ -641,7 +641,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>8.81</v>
+        <v>88.06</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-29 11:01</t>
+    <t xml:space="preserve">2026-10-01 19:26</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -87,7 +87,7 @@
     <t xml:space="preserve">Indicador</t>
   </si>
   <si>
-    <t xml:space="preserve">Movilidad interna (CMI)</t>
+    <t xml:space="preserve">Movilidad interna comunal (CMI)</t>
   </si>
   <si>
     <t xml:space="preserve">Unidad territorial</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 19:26</t>
+    <t xml:space="preserve">2026-10-02 13:05</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
+++ b/output/graficos_dimensiones/comunal_m_movinterna_a_2022_antofagasta.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:05</t>
+    <t xml:space="preserve">2026-10-05 07:28</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
